--- a/public/energiaai-rendszerimport-sablon.xlsx
+++ b/public/energiaai-rendszerimport-sablon.xlsx
@@ -6,7 +6,7 @@
   <sheets>
     <sheet sheetId="1" name="Rendszerleltár" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Rendszertípusok" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Aktív funkciók" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Eszköz funkciók" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Engedélyezett értékek" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
@@ -17,12 +17,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="114">
   <si>
     <t>EnergiaAI Kontroll – általános MI-rendszerimport</t>
   </si>
   <si>
-    <t>Egy sor egy MI-rendszer. Az aktív funkciókódokat | jellel válaszd el. A fejlécet ne módosítsd; használati profil nem szükséges.</t>
+    <t>Egy sor egy MI-rendszer. Az eszköz funkciók kódjait | jellel válaszd el. A fejlécet ne módosítsd. Az utolsó négy oszlop nyilatkozat: a szokásos eset Igen, a szabályozott termék Nem.</t>
   </si>
   <si>
     <t>Rendszer neve</t>
@@ -37,7 +37,7 @@
     <t>Rendeltetés</t>
   </si>
   <si>
-    <t>Aktív funkciókódok</t>
+    <t>Eszköz funkciók kódjai</t>
   </si>
   <si>
     <t>Szervezeti szerep</t>
@@ -46,6 +46,18 @@
     <t>Életciklus</t>
   </si>
   <si>
+    <t>EU-ban használják</t>
+  </si>
+  <si>
+    <t>MI-használat egyértelmű</t>
+  </si>
+  <si>
+    <t>Nincs tiltott gyakorlat</t>
+  </si>
+  <si>
+    <t>Szabályozott termékbe épül</t>
+  </si>
+  <si>
     <t>Belső tudásasszisztens</t>
   </si>
   <si>
@@ -67,6 +79,12 @@
     <t>pilot</t>
   </si>
   <si>
+    <t>Igen</t>
+  </si>
+  <si>
+    <t>Nem</t>
+  </si>
+  <si>
     <t>Számlafeldolgozó MI</t>
   </si>
   <si>
@@ -329,6 +347,18 @@
   </si>
   <si>
     <t>planned | development | testing | pilot | production | suspended | retired</t>
+  </si>
+  <si>
+    <t>Igen | Nem — a szokásos eset Igen</t>
+  </si>
+  <si>
+    <t>Igen | Nem — egyértelmű-e a felhasználónak, hogy MI-vel kommunikál</t>
+  </si>
+  <si>
+    <t>Igen | Nem — Nem esetén figyelmeztetés kerül a szabályzatba</t>
+  </si>
+  <si>
+    <t>Igen | Nem — orvostechnikai eszköz, gép, jármű, játék. Igen esetén magas kockázatú.</t>
   </si>
 </sst>
 </file>
@@ -766,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -774,10 +804,11 @@
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="58" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,8 +818,12 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-    </row>
-    <row r="2" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -798,8 +833,12 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="4" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="4" ht="38" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -821,77 +860,125 @@
       <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -899,8 +986,12 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -908,8 +999,12 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -917,8 +1012,12 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-    </row>
-    <row r="11" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -926,8 +1025,12 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-    </row>
-    <row r="12" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -935,8 +1038,12 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -944,8 +1051,12 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-    </row>
-    <row r="14" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -953,8 +1064,12 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-    </row>
-    <row r="15" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -962,8 +1077,12 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-    </row>
-    <row r="16" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -971,8 +1090,12 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -980,8 +1103,12 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-    </row>
-    <row r="18" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -989,8 +1116,12 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-    </row>
-    <row r="19" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -998,8 +1129,12 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-    </row>
-    <row r="20" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1007,8 +1142,12 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-    </row>
-    <row r="21" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1016,8 +1155,12 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-    </row>
-    <row r="22" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1025,8 +1168,12 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
-    </row>
-    <row r="23" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1034,8 +1181,12 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-    </row>
-    <row r="24" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1043,8 +1194,12 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-    </row>
-    <row r="25" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1052,8 +1207,12 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-    </row>
-    <row r="26" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1061,8 +1220,12 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-    </row>
-    <row r="27" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1070,8 +1233,12 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
-    </row>
-    <row r="28" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1079,8 +1246,12 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-    </row>
-    <row r="29" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1088,8 +1259,12 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1097,8 +1272,12 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
-    </row>
-    <row r="31" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+    </row>
+    <row r="31" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1106,8 +1285,12 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-    </row>
-    <row r="32" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -1115,8 +1298,12 @@
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
-    </row>
-    <row r="33" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1124,8 +1311,12 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-    </row>
-    <row r="34" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -1133,8 +1324,12 @@
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
-    </row>
-    <row r="35" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1142,8 +1337,12 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
-    </row>
-    <row r="36" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="36" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -1151,8 +1350,12 @@
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
-    </row>
-    <row r="37" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1160,8 +1363,12 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
-    </row>
-    <row r="38" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -1169,8 +1376,12 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
-    </row>
-    <row r="39" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+    </row>
+    <row r="39" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1178,8 +1389,12 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
-    </row>
-    <row r="40" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -1187,8 +1402,12 @@
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
-    </row>
-    <row r="41" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+    </row>
+    <row r="41" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1196,8 +1415,12 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
-    </row>
-    <row r="42" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -1205,8 +1428,12 @@
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
-    </row>
-    <row r="43" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+    </row>
+    <row r="43" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1214,8 +1441,12 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
-    </row>
-    <row r="44" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+    </row>
+    <row r="44" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -1223,8 +1454,12 @@
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
-    </row>
-    <row r="45" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+    </row>
+    <row r="45" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1232,8 +1467,12 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
-    </row>
-    <row r="46" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+    </row>
+    <row r="46" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -1241,8 +1480,12 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
-    </row>
-    <row r="47" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+    </row>
+    <row r="47" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1250,8 +1493,12 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
-    </row>
-    <row r="48" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -1259,8 +1506,12 @@
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
-    </row>
-    <row r="49" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+    </row>
+    <row r="49" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -1268,8 +1519,12 @@
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
-    </row>
-    <row r="50" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -1277,8 +1532,12 @@
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
-    </row>
-    <row r="51" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+    </row>
+    <row r="51" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -1286,8 +1545,12 @@
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
-    </row>
-    <row r="52" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -1295,8 +1558,12 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
-    </row>
-    <row r="53" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+    </row>
+    <row r="53" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -1304,8 +1571,12 @@
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
-    </row>
-    <row r="54" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -1313,8 +1584,12 @@
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
-    </row>
-    <row r="55" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+    </row>
+    <row r="55" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -1322,8 +1597,12 @@
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
-    </row>
-    <row r="56" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+    </row>
+    <row r="56" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -1331,8 +1610,12 @@
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
-    </row>
-    <row r="57" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+    </row>
+    <row r="57" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1340,8 +1623,12 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
-    </row>
-    <row r="58" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -1349,8 +1636,12 @@
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
-    </row>
-    <row r="59" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+    </row>
+    <row r="59" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -1358,8 +1649,12 @@
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
-    </row>
-    <row r="60" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -1367,8 +1662,12 @@
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
-    </row>
-    <row r="61" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+    </row>
+    <row r="61" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -1376,8 +1675,12 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
-    </row>
-    <row r="62" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -1385,8 +1688,12 @@
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
-    </row>
-    <row r="63" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+    </row>
+    <row r="63" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -1394,8 +1701,12 @@
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
-    </row>
-    <row r="64" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+    </row>
+    <row r="64" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -1403,8 +1714,12 @@
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
-    </row>
-    <row r="65" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+    </row>
+    <row r="65" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -1412,8 +1727,12 @@
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-    </row>
-    <row r="66" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+    </row>
+    <row r="66" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -1421,8 +1740,12 @@
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
-    </row>
-    <row r="67" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+    </row>
+    <row r="67" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -1430,8 +1753,12 @@
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
-    </row>
-    <row r="68" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+    </row>
+    <row r="68" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -1439,8 +1766,12 @@
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
-    </row>
-    <row r="69" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+    </row>
+    <row r="69" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -1448,8 +1779,12 @@
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
-    </row>
-    <row r="70" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+    </row>
+    <row r="70" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -1457,8 +1792,12 @@
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
-    </row>
-    <row r="71" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+    </row>
+    <row r="71" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -1466,8 +1805,12 @@
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
-    </row>
-    <row r="72" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+    </row>
+    <row r="72" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -1475,8 +1818,12 @@
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
-    </row>
-    <row r="73" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+    </row>
+    <row r="73" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -1484,8 +1831,12 @@
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
-    </row>
-    <row r="74" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+    </row>
+    <row r="74" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -1493,8 +1844,12 @@
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
-    </row>
-    <row r="75" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -1502,8 +1857,12 @@
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
-    </row>
-    <row r="76" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+    </row>
+    <row r="76" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -1511,8 +1870,12 @@
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
-    </row>
-    <row r="77" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+    </row>
+    <row r="77" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -1520,8 +1883,12 @@
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
-    </row>
-    <row r="78" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+    </row>
+    <row r="78" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -1529,8 +1896,12 @@
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
-    </row>
-    <row r="79" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+    </row>
+    <row r="79" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -1538,8 +1909,12 @@
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
-    </row>
-    <row r="80" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+    </row>
+    <row r="80" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -1547,8 +1922,12 @@
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
-    </row>
-    <row r="81" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+    </row>
+    <row r="81" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -1556,8 +1935,12 @@
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
-    </row>
-    <row r="82" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+    </row>
+    <row r="82" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -1565,8 +1948,12 @@
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
-    </row>
-    <row r="83" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+    </row>
+    <row r="83" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -1574,8 +1961,12 @@
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
-    </row>
-    <row r="84" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+    </row>
+    <row r="84" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -1583,8 +1974,12 @@
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
-    </row>
-    <row r="85" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+    </row>
+    <row r="85" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -1592,8 +1987,12 @@
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
-    </row>
-    <row r="86" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+    </row>
+    <row r="86" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -1601,8 +2000,12 @@
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
-    </row>
-    <row r="87" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+    </row>
+    <row r="87" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -1610,8 +2013,12 @@
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
-    </row>
-    <row r="88" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+    </row>
+    <row r="88" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -1619,8 +2026,12 @@
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
-    </row>
-    <row r="89" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+    </row>
+    <row r="89" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -1628,8 +2039,12 @@
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
-    </row>
-    <row r="90" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+    </row>
+    <row r="90" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -1637,8 +2052,12 @@
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
-    </row>
-    <row r="91" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+    </row>
+    <row r="91" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -1646,8 +2065,12 @@
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
-    </row>
-    <row r="92" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+    </row>
+    <row r="92" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -1655,8 +2078,12 @@
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
-    </row>
-    <row r="93" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+    </row>
+    <row r="93" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -1664,8 +2091,12 @@
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
-    </row>
-    <row r="94" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+    </row>
+    <row r="94" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -1673,8 +2104,12 @@
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
-    </row>
-    <row r="95" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+    </row>
+    <row r="95" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -1682,8 +2117,12 @@
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
-    </row>
-    <row r="96" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+    </row>
+    <row r="96" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -1691,8 +2130,12 @@
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
-    </row>
-    <row r="97" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+    </row>
+    <row r="97" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -1700,8 +2143,12 @@
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
-    </row>
-    <row r="98" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+    </row>
+    <row r="98" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -1709,8 +2156,12 @@
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
-    </row>
-    <row r="99" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+    </row>
+    <row r="99" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -1718,8 +2169,12 @@
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
-    </row>
-    <row r="100" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+    </row>
+    <row r="100" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -1727,8 +2182,12 @@
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
-    </row>
-    <row r="101" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+    </row>
+    <row r="101" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -1736,8 +2195,12 @@
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
-    </row>
-    <row r="102" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+    </row>
+    <row r="102" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -1745,8 +2208,12 @@
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
-    </row>
-    <row r="103" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
+    </row>
+    <row r="103" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -1754,8 +2221,12 @@
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
-    </row>
-    <row r="104" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+    </row>
+    <row r="104" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -1763,14 +2234,18 @@
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G104"/>
+  <autoFilter ref="A4:K104"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <dataValidations count="8">
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Válassz érvényes rendszertípuskódot." sqref="B10:B104">
       <formula1>RendszerTipusKodok</formula1>
     </dataValidation>
@@ -1795,6 +2270,12 @@
     <dataValidation type="list" sqref="G5:G104">
       <formula1>"planned,development,testing,pilot,production,suspended,retired"</formula1>
     </dataValidation>
+    <dataValidation type="list" sqref="H10:K104">
+      <formula1>"Igen,Nem"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H5:K104">
+      <formula1>"Igen,Nem"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1815,103 +2296,103 @@
         <v>3</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1934,338 +2415,338 @@
   <sheetData>
     <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2277,7 +2758,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2286,10 +2767,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2297,7 +2778,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2305,7 +2786,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2313,7 +2794,39 @@
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
